--- a/data/trans_orig/P23_1_2016_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco actual o pasado en 2016</t>
+          <t>Población según el consumo de tabaco actual o pasado en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>264354</t>
+          <t>262805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>317445</t>
+          <t>316716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>782595</t>
+          <t>780563</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>831147</t>
+          <t>833736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1055668</t>
+          <t>1055490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1135239</t>
+          <t>1136592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215453</t>
+          <t>217320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265417</t>
+          <t>266856</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>35961</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>64097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>260231</t>
+          <t>260621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>321536</t>
+          <t>320432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25822</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>23299</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>30193</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>20724</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>42741</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>2,45%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>30193</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>20868</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>43768</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183214</t>
+          <t>183524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231854</t>
+          <t>233544</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103193</t>
+          <t>101413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144425</t>
+          <t>145491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>298490</t>
+          <t>295563</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>362635</t>
+          <t>364620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>868634</t>
+          <t>865656</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>959757</t>
+          <t>959997</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1048123</t>
+          <t>1048970</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1137533</t>
+          <t>1138904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1936253</t>
+          <t>1933938</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2065335</t>
+          <t>2070944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>324046</t>
+          <t>322922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>394655</t>
+          <t>392545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204093</t>
+          <t>202647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>265709</t>
+          <t>262482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>547926</t>
+          <t>543171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>640196</t>
+          <t>638669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35839</t>
+          <t>35692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63073</t>
+          <t>63035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30135</t>
+          <t>31028</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54823</t>
+          <t>55598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72331</t>
+          <t>73477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111120</t>
+          <t>110482</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>716074</t>
+          <t>711892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>802696</t>
+          <t>801065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>580664</t>
+          <t>579989</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659785</t>
+          <t>661590</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1321481</t>
+          <t>1313801</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1438469</t>
+          <t>1441145</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282203</t>
+          <t>283374</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>331362</t>
+          <t>330178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>302619</t>
+          <t>298841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349289</t>
+          <t>346706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>597737</t>
+          <t>596003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>664122</t>
+          <t>663334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84072</t>
+          <t>81781</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121454</t>
+          <t>121551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84734</t>
+          <t>85840</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124410</t>
+          <t>125316</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176563</t>
+          <t>179473</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>230561</t>
+          <t>232846</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28362</t>
+          <t>29079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>27901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25859</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50250</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99301</t>
+          <t>99798</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138170</t>
+          <t>140384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84619</t>
+          <t>84279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121009</t>
+          <t>120516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>195037</t>
+          <t>194275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>250394</t>
+          <t>249585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1449418</t>
+          <t>1447954</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1566198</t>
+          <t>1564856</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2159202</t>
+          <t>2169510</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2280640</t>
+          <t>2286543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3646102</t>
+          <t>3649374</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3816750</t>
+          <t>3825268</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>652949</t>
+          <t>650518</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>749727</t>
+          <t>750855</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>347254</t>
+          <t>349829</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>425013</t>
+          <t>428037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1026810</t>
+          <t>1022427</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1145799</t>
+          <t>1147266</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67341</t>
+          <t>66595</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104337</t>
+          <t>103063</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57668</t>
+          <t>58138</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91633</t>
+          <t>92860</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>133015</t>
+          <t>133172</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>183848</t>
+          <t>185901</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1030368</t>
+          <t>1022482</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1139003</t>
+          <t>1138288</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>796893</t>
+          <t>794214</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>898087</t>
+          <t>894513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1854073</t>
+          <t>1846492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2005395</t>
+          <t>2005149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco actual o pasado en 2023</t>
+          <t>Población según el consumo de tabaco actual o pasado en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>185565</t>
+          <t>186286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>227103</t>
+          <t>229059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>614442</t>
+          <t>614600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>647057</t>
+          <t>646577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>809161</t>
+          <t>811859</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>866788</t>
+          <t>867061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>148656</t>
+          <t>148895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187891</t>
+          <t>184772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35483</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56068</t>
+          <t>56434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188552</t>
+          <t>188856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233449</t>
+          <t>235246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17061</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3479,47 +3479,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>7029</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12027</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7029</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12090</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26422</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115177</t>
+          <t>115011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153764</t>
+          <t>154591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60887</t>
+          <t>60508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86486</t>
+          <t>84694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>183435</t>
+          <t>182837</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>227934</t>
+          <t>228724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>802944</t>
+          <t>856463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1309021</t>
+          <t>1310207</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1464909</t>
+          <t>1471344</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1741785</t>
+          <t>1733980</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2281983</t>
+          <t>2270076</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2972805</t>
+          <t>2987008</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,01%</t>
         </is>
       </c>
     </row>
@@ -3920,12 +3920,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>324631</t>
+          <t>324738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1079570</t>
+          <t>981371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>146799</t>
+          <t>157962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>240247</t>
+          <t>242287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>507394</t>
+          <t>502168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1419786</t>
+          <t>1425195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -4033,12 +4033,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34358</t>
+          <t>34979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83959</t>
+          <t>82854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4048,82 +4048,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>37878</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26562</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>54635</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>94124</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>67718</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>127807</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>1,5%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37878</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26435</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>54916</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>94124</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>66059</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>125777</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>372178</t>
+          <t>395299</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>615322</t>
+          <t>615360</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314858</t>
+          <t>323437</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>495639</t>
+          <t>492772</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>784526</t>
+          <t>765323</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1082450</t>
+          <t>1083735</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4376,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>374209</t>
+          <t>373136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>429429</t>
+          <t>430210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>442730</t>
+          <t>442095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>484307</t>
+          <t>484235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>831945</t>
+          <t>832252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>898681</t>
+          <t>898981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -4489,12 +4489,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119177</t>
+          <t>118254</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>163190</t>
+          <t>161052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73528</t>
+          <t>72860</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103647</t>
+          <t>102372</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4539,12 +4539,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>201128</t>
+          <t>202373</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>251239</t>
+          <t>251506</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4602,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15453</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>32468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4652,12 +4652,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42886</t>
+          <t>42506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74171</t>
+          <t>75737</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121339</t>
+          <t>125843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69407</t>
+          <t>68281</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>99566</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>156414</t>
+          <t>153811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>211459</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -4945,12 +4945,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1371682</t>
+          <t>1324364</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1921483</t>
+          <t>1920010</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2576791</t>
+          <t>2574702</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2836207</t>
+          <t>2837726</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3925592</t>
+          <t>3977585</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4674720</t>
+          <t>4658295</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -5058,12 +5058,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>635396</t>
+          <t>639367</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1414674</t>
+          <t>1478840</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>278900</t>
+          <t>278125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375939</t>
+          <t>375943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>940672</t>
+          <t>946471</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1944120</t>
+          <t>1852348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -5171,12 +5171,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50937</t>
+          <t>49347</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104059</t>
+          <t>101412</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>52842</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85435</t>
+          <t>87550</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5241,12 +5241,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>111771</t>
+          <t>112297</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>174558</t>
+          <t>173755</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>603599</t>
+          <t>593996</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>845389</t>
+          <t>840626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>482203</t>
+          <t>488534</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>642800</t>
+          <t>643441</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1164015</t>
+          <t>1162198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1459076</t>
+          <t>1450216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_1_2016_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>262805</t>
+          <t>261637</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>316716</t>
+          <t>314372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>780563</t>
+          <t>780325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>833736</t>
+          <t>833189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1055490</t>
+          <t>1055140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1136592</t>
+          <t>1137003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>217320</t>
+          <t>217415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266856</t>
+          <t>266229</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35961</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64097</t>
+          <t>62230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>260621</t>
+          <t>259567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>320432</t>
+          <t>319568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25626</t>
+          <t>26833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42741</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183524</t>
+          <t>184974</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233544</t>
+          <t>233720</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101413</t>
+          <t>104907</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145491</t>
+          <t>148077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>295563</t>
+          <t>302782</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>364620</t>
+          <t>365139</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>865656</t>
+          <t>868913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>959997</t>
+          <t>961233</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1048970</t>
+          <t>1049738</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1138904</t>
+          <t>1138397</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1933938</t>
+          <t>1945125</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2070944</t>
+          <t>2070755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>322922</t>
+          <t>322542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>392545</t>
+          <t>393381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202647</t>
+          <t>205177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>262482</t>
+          <t>260051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>543171</t>
+          <t>545689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>638669</t>
+          <t>636324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>35421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63035</t>
+          <t>65693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>30681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55598</t>
+          <t>57557</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73477</t>
+          <t>71910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110482</t>
+          <t>110333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>711892</t>
+          <t>714044</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>801065</t>
+          <t>799332</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>579989</t>
+          <t>576681</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>661590</t>
+          <t>660066</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1313801</t>
+          <t>1315362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1441145</t>
+          <t>1436117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283374</t>
+          <t>283323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>330178</t>
+          <t>333892</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>298841</t>
+          <t>297436</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>346706</t>
+          <t>344052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>596003</t>
+          <t>598488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>663334</t>
+          <t>664402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,73%</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>83569</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121551</t>
+          <t>122058</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85840</t>
+          <t>87947</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125316</t>
+          <t>126586</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>179473</t>
+          <t>178053</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>232846</t>
+          <t>230873</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>28196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27901</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>26152</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49788</t>
+          <t>49583</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99798</t>
+          <t>99723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140384</t>
+          <t>142116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84279</t>
+          <t>86396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120516</t>
+          <t>122935</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194275</t>
+          <t>194852</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249585</t>
+          <t>248211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1447954</t>
+          <t>1457599</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1564856</t>
+          <t>1568753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2169510</t>
+          <t>2160752</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2286543</t>
+          <t>2288022</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3649374</t>
+          <t>3655538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3825268</t>
+          <t>3821474</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,36%</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>650518</t>
+          <t>650448</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>750855</t>
+          <t>746644</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>349829</t>
+          <t>348857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>428037</t>
+          <t>426510</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1022427</t>
+          <t>1024598</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1147266</t>
+          <t>1147161</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66595</t>
+          <t>65675</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>103063</t>
+          <t>104641</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58138</t>
+          <t>56808</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92860</t>
+          <t>90274</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,47 +2714,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>156430</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>132585</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>181742</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>2,63%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>156430</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>133172</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>185901</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1022482</t>
+          <t>1024829</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1138288</t>
+          <t>1135964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>794214</t>
+          <t>790721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>894513</t>
+          <t>898701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1846492</t>
+          <t>1860565</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2005149</t>
+          <t>2001384</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -3233,32 +3233,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>207050</t>
+          <t>248828</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>186286</t>
+          <t>224248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>229059</t>
+          <t>272648</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3268,32 +3268,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>631730</t>
+          <t>688169</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>614600</t>
+          <t>670759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>646577</t>
+          <t>704767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3303,32 +3303,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>838780</t>
+          <t>936997</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>811859</t>
+          <t>905128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>867061</t>
+          <t>969647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -3346,32 +3346,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>166717</t>
+          <t>177221</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>148895</t>
+          <t>156002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184772</t>
+          <t>198340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3381,32 +3381,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44933</t>
+          <t>47704</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35260</t>
+          <t>38037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56434</t>
+          <t>60491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3416,32 +3416,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>211650</t>
+          <t>224925</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188856</t>
+          <t>200931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>235246</t>
+          <t>250524</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -3459,32 +3459,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>16726</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3494,32 +3494,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3529,32 +3529,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24765</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3572,32 +3572,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>133675</t>
+          <t>145352</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115011</t>
+          <t>125299</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154591</t>
+          <t>167735</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3607,32 +3607,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71816</t>
+          <t>78237</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60508</t>
+          <t>64627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84694</t>
+          <t>91081</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3642,32 +3642,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>205492</t>
+          <t>223589</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>182837</t>
+          <t>200174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>228724</t>
+          <t>248560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -3685,17 +3685,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3755,17 +3755,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3802,32 +3802,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1153794</t>
+          <t>1256629</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>856463</t>
+          <t>1205038</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1310207</t>
+          <t>1316795</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3837,32 +3837,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1568882</t>
+          <t>1445591</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1471344</t>
+          <t>1403066</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1733980</t>
+          <t>1486001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3872,32 +3872,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2722677</t>
+          <t>2702220</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2270076</t>
+          <t>2634687</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2987008</t>
+          <t>2764690</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>62,86%</t>
         </is>
       </c>
     </row>
@@ -3915,32 +3915,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>545224</t>
+          <t>333396</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>324738</t>
+          <t>300399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>981371</t>
+          <t>366096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3950,32 +3950,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>203124</t>
+          <t>222123</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157962</t>
+          <t>197738</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>242287</t>
+          <t>246998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3985,32 +3985,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>748348</t>
+          <t>555519</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>502168</t>
+          <t>510898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1425195</t>
+          <t>596085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -4028,32 +4028,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56246</t>
+          <t>60081</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34979</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82854</t>
+          <t>85485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4063,32 +4063,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37878</t>
+          <t>42947</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t>31917</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54635</t>
+          <t>57910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4098,32 +4098,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>94124</t>
+          <t>103027</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67718</t>
+          <t>81080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127807</t>
+          <t>131173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -4141,32 +4141,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533031</t>
+          <t>578238</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>395299</t>
+          <t>528606</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>615360</t>
+          <t>622596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4176,32 +4176,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>426594</t>
+          <t>459324</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>323437</t>
+          <t>425900</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>492772</t>
+          <t>499739</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4211,32 +4211,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>959625</t>
+          <t>1037561</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>765323</t>
+          <t>981907</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1083735</t>
+          <t>1093180</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -4254,17 +4254,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2288294</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2288294</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2288294</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4289,17 +4289,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2236479</t>
+          <t>2169984</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2236479</t>
+          <t>2169984</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2236479</t>
+          <t>2169984</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4524774</t>
+          <t>4398327</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4524774</t>
+          <t>4398327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4524774</t>
+          <t>4398327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4371,32 +4371,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>404756</t>
+          <t>451436</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>373136</t>
+          <t>426764</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>430210</t>
+          <t>476291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4406,32 +4406,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>463401</t>
+          <t>519436</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>442095</t>
+          <t>496176</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>484235</t>
+          <t>540513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4441,32 +4441,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>868158</t>
+          <t>970872</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>832252</t>
+          <t>935689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>898981</t>
+          <t>1003995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -4484,32 +4484,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138425</t>
+          <t>149869</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118254</t>
+          <t>129120</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>161052</t>
+          <t>174023</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4519,32 +4519,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87092</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72860</t>
+          <t>81526</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102372</t>
+          <t>113049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4554,32 +4554,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>225517</t>
+          <t>245458</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>202373</t>
+          <t>222141</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>251506</t>
+          <t>273753</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -4597,32 +4597,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4632,32 +4632,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>25859</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32468</t>
+          <t>35990</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4667,32 +4667,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>32073</t>
+          <t>38338</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42506</t>
+          <t>50383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -4710,32 +4710,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94829</t>
+          <t>97803</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75737</t>
+          <t>79969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125843</t>
+          <t>116469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4745,32 +4745,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>83947</t>
+          <t>91530</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68281</t>
+          <t>76186</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99566</t>
+          <t>109130</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4780,32 +4780,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>178777</t>
+          <t>189332</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153811</t>
+          <t>164814</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211459</t>
+          <t>216888</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -4823,17 +4823,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>657901</t>
+          <t>732414</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>657901</t>
+          <t>732414</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>657901</t>
+          <t>732414</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4893,17 +4893,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1304525</t>
+          <t>1444001</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1304525</t>
+          <t>1444001</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1304525</t>
+          <t>1444001</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4940,32 +4940,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1765600</t>
+          <t>1956893</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1324364</t>
+          <t>1894088</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1920010</t>
+          <t>2029008</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4975,32 +4975,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2664014</t>
+          <t>2653195</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2574702</t>
+          <t>2598189</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2837726</t>
+          <t>2696318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5010,32 +5010,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4429615</t>
+          <t>4610089</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3977585</t>
+          <t>4526691</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4658295</t>
+          <t>4688576</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -5053,32 +5053,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>850366</t>
+          <t>660485</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>639367</t>
+          <t>612617</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1478840</t>
+          <t>710516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5088,32 +5088,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>335149</t>
+          <t>365417</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>278125</t>
+          <t>332989</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375943</t>
+          <t>400495</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5123,32 +5123,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1185515</t>
+          <t>1025902</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>946471</t>
+          <t>974580</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1852348</t>
+          <t>1085832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -5166,32 +5166,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72354</t>
+          <t>79688</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49347</t>
+          <t>60811</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101412</t>
+          <t>108621</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5201,32 +5201,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68368</t>
+          <t>76733</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52842</t>
+          <t>60961</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>87550</t>
+          <t>93739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5236,32 +5236,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140722</t>
+          <t>156421</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>112297</t>
+          <t>128840</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>173755</t>
+          <t>185941</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -5279,32 +5279,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>761535</t>
+          <t>821392</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>593996</t>
+          <t>767147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>840626</t>
+          <t>878450</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5314,32 +5314,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>582358</t>
+          <t>629091</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>488534</t>
+          <t>589261</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>643441</t>
+          <t>671315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5349,32 +5349,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1343893</t>
+          <t>1450483</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1162198</t>
+          <t>1385134</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1450216</t>
+          <t>1518184</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -5392,17 +5392,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3449856</t>
+          <t>3518459</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3449856</t>
+          <t>3518459</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3449856</t>
+          <t>3518459</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5427,17 +5427,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3649888</t>
+          <t>3724435</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3649888</t>
+          <t>3724435</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3649888</t>
+          <t>3724435</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5462,17 +5462,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7099745</t>
+          <t>7242895</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7099745</t>
+          <t>7242895</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7099745</t>
+          <t>7242895</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
